--- a/data/k-props/2026-08-27.xlsx
+++ b/data/k-props/2026-08-27.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
   <si>
     <t>date</t>
   </si>
@@ -142,21 +142,39 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Gordon Graceffo</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Yankees</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Yankees</t>
-  </si>
-  <si>
     <t>Gerrit Cole</t>
   </si>
   <si>
@@ -169,18 +187,21 @@
     <t>Kansas City Royals @ Toronto Blue Jays</t>
   </si>
   <si>
+    <t>Spencer Arrighetti</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ New York Mets</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
     <t>Sean Manaea</t>
   </si>
   <si>
-    <t>Milwaukee Brewers @ New York Mets</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
     <t>Yoshinobu Yamamoto</t>
   </si>
   <si>
@@ -190,28 +211,16 @@
     <t>Chris Sale</t>
   </si>
   <si>
+    <t>Jose Cabrera</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
     <t>Landen Roupp</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Jose Cabrera</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Spencer Arrighetti</t>
   </si>
 </sst>
 </file>
@@ -592,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AM15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -728,10 +737,10 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-154</v>
+        <v>-118</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -752,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>0.205</v>
@@ -776,10 +785,10 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2255</v>
+        <v>0.1851</v>
       </c>
       <c r="U2">
-        <v>0.1985</v>
+        <v>0.1932</v>
       </c>
       <c r="V2">
         <v>9</v>
@@ -788,10 +797,10 @@
         <v>0.1866</v>
       </c>
       <c r="X2">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y2">
-        <v>0.9901</v>
+        <v>0.9253</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -800,7 +809,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.46</v>
+        <v>4.26</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -809,13 +818,13 @@
         <v>0.2243</v>
       </c>
       <c r="AG2">
-        <v>1.0613</v>
+        <v>0.8856</v>
       </c>
       <c r="AH2">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>5.66</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -825,26 +834,17 @@
       <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-      <c r="D3">
-        <v>132</v>
-      </c>
-      <c r="E3">
-        <v>-170</v>
-      </c>
       <c r="F3" t="s">
         <v>47</v>
       </c>
       <c r="G3">
-        <v>823503</v>
+        <v>822694</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -853,46 +853,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0.1947</v>
+        <v>0.1832</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>4.08</v>
+        <v>4.37</v>
       </c>
       <c r="Q3">
-        <v>0.1947</v>
+        <v>0.1522</v>
       </c>
       <c r="R3">
-        <v>0.361</v>
+        <v>0.315</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2366</v>
+        <v>0.209</v>
       </c>
       <c r="U3">
-        <v>0.245</v>
+        <v>0.2181</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2467</v>
+        <v>0.2065</v>
       </c>
       <c r="X3">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y3">
-        <v>0.9956</v>
+        <v>0.9749</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -901,22 +901,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.88</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1947</v>
+        <v>0.1735</v>
       </c>
       <c r="AG3">
-        <v>1.1135</v>
+        <v>1</v>
       </c>
       <c r="AH3">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>5.08</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -926,26 +926,17 @@
       <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-      <c r="D4">
-        <v>-113</v>
-      </c>
-      <c r="E4">
-        <v>-113</v>
-      </c>
       <c r="F4" t="s">
         <v>47</v>
       </c>
       <c r="G4">
-        <v>823503</v>
+        <v>822694</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -954,46 +945,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.266</v>
+        <v>0.2232</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="P4">
-        <v>4.06</v>
+        <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>0.281</v>
+        <v>0.1856</v>
       </c>
       <c r="R4">
-        <v>0.377</v>
+        <v>0.327</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2222</v>
+        <v>0.228</v>
       </c>
       <c r="U4">
-        <v>0.2138</v>
+        <v>0.2042</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2194</v>
+        <v>0.2183</v>
       </c>
       <c r="X4">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y4">
-        <v>0.9937</v>
+        <v>1.026</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1002,22 +993,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>6.63</v>
+        <v>4.79</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2716</v>
+        <v>0.2109</v>
       </c>
       <c r="AG4">
-        <v>1.0456</v>
+        <v>1.0908</v>
       </c>
       <c r="AH4">
-        <v>-0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>6.42</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1025,76 +1016,55 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5">
+        <v>823014</v>
+      </c>
+      <c r="H5" t="s">
         <v>50</v>
       </c>
-      <c r="C5">
+      <c r="I5">
         <v>4.5</v>
       </c>
-      <c r="D5">
-        <v>-134</v>
-      </c>
-      <c r="E5">
-        <v>105</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5">
-        <v>822771</v>
-      </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5">
-        <v>5.7</v>
-      </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.2133</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>127</v>
+        <v>0.1502</v>
       </c>
       <c r="P5">
-        <v>4.19</v>
-      </c>
-      <c r="Q5">
-        <v>0.2205</v>
-      </c>
-      <c r="R5">
-        <v>0.388</v>
+        <v>3.99</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1891</v>
+        <v>0.2621</v>
       </c>
       <c r="U5">
-        <v>0.1766</v>
+        <v>0.2395</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2092</v>
+        <v>0.2361</v>
       </c>
       <c r="X5">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y5">
-        <v>0.9815</v>
+        <v>1.0654</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1103,22 +1073,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.49</v>
+        <v>3.61</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2161</v>
+        <v>0.1502</v>
       </c>
       <c r="AG5">
-        <v>0.8899</v>
+        <v>1.2541</v>
       </c>
       <c r="AH5">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>4.69</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1126,28 +1096,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-160</v>
+        <v>132</v>
       </c>
       <c r="E6">
-        <v>126</v>
+        <v>-170</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>823581</v>
+        <v>823503</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1156,46 +1126,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>0.2312</v>
+        <v>0.1947</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="P6">
-        <v>4.32</v>
+        <v>4.08</v>
       </c>
       <c r="Q6">
-        <v>0.2558</v>
+        <v>0.1947</v>
       </c>
       <c r="R6">
-        <v>0.392</v>
+        <v>0.361</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T6">
-        <v>0.1981</v>
+        <v>0.2366</v>
       </c>
       <c r="U6">
-        <v>0.2214</v>
+        <v>0.245</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2194</v>
+        <v>0.2467</v>
       </c>
       <c r="X6">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y6">
-        <v>0.9848</v>
+        <v>0.9947</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1204,22 +1174,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.44</v>
+        <v>4.95</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2409</v>
+        <v>0.1947</v>
       </c>
       <c r="AG6">
-        <v>0.9322</v>
+        <v>1.1319</v>
       </c>
       <c r="AH6">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AM6">
-        <v>5.64</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1230,25 +1200,25 @@
         <v>54</v>
       </c>
       <c r="C7">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="E7">
-        <v>-109</v>
+        <v>-113</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
-        <v>823581</v>
+        <v>823503</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1257,46 +1227,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>0.3927</v>
+        <v>0.266</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="P7">
-        <v>3.79</v>
+        <v>4.06</v>
       </c>
       <c r="Q7">
-        <v>0.3874</v>
+        <v>0.281</v>
       </c>
       <c r="R7">
-        <v>0.357</v>
+        <v>0.377</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T7">
-        <v>0.2272</v>
+        <v>0.2222</v>
       </c>
       <c r="U7">
-        <v>0.2221</v>
+        <v>0.2138</v>
       </c>
       <c r="V7">
         <v>8</v>
       </c>
       <c r="W7">
-        <v>0.2231</v>
+        <v>0.2194</v>
       </c>
       <c r="X7">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y7">
-        <v>0.9806</v>
+        <v>0.994</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1305,22 +1275,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>9.39</v>
+        <v>6.74</v>
       </c>
       <c r="AE7" t="s">
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>0.3908</v>
+        <v>0.2716</v>
       </c>
       <c r="AG7">
-        <v>1.0695</v>
+        <v>1.0628</v>
       </c>
       <c r="AH7">
-        <v>-0.91</v>
+        <v>-0.57</v>
       </c>
       <c r="AM7">
-        <v>8.48</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1331,25 +1301,25 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-162</v>
+        <v>-134</v>
       </c>
       <c r="E8">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
         <v>57</v>
       </c>
       <c r="G8">
-        <v>824879</v>
+        <v>822771</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1358,46 +1328,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>0.2487</v>
+        <v>0.2133</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P8">
-        <v>3.84</v>
+        <v>4.19</v>
       </c>
       <c r="Q8">
-        <v>0.25</v>
+        <v>0.2205</v>
       </c>
       <c r="R8">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T8">
-        <v>0.2292</v>
+        <v>0.1891</v>
       </c>
       <c r="U8">
-        <v>0.2249</v>
+        <v>0.1766</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2196</v>
+        <v>0.2092</v>
       </c>
       <c r="X8">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y8">
-        <v>1.0066</v>
+        <v>0.981</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1406,22 +1376,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>6.86</v>
+        <v>4.56</v>
       </c>
       <c r="AE8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2492</v>
+        <v>0.2161</v>
       </c>
       <c r="AG8">
-        <v>1.0786</v>
+        <v>0.9045</v>
       </c>
       <c r="AH8">
-        <v>-0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>6.65</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1431,26 +1401,17 @@
       <c r="B9" t="s">
         <v>58</v>
       </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-      <c r="D9">
-        <v>130</v>
-      </c>
-      <c r="E9">
-        <v>-151</v>
-      </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9">
-        <v>824879</v>
+        <v>822771</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1459,46 +1420,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0.3063</v>
+        <v>0.2269</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="P9">
-        <v>4.01</v>
+        <v>4.39</v>
       </c>
       <c r="Q9">
-        <v>0.3707</v>
+        <v>0.2043</v>
       </c>
       <c r="R9">
-        <v>0.367</v>
+        <v>0.317</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T9">
-        <v>0.224</v>
+        <v>0.1701</v>
       </c>
       <c r="U9">
-        <v>0.1967</v>
+        <v>0.1861</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2013</v>
+        <v>0.2078</v>
       </c>
       <c r="X9">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y9">
-        <v>1.002</v>
+        <v>0.9637</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1507,22 +1468,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>8.21</v>
+        <v>3.92</v>
       </c>
       <c r="AE9" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.3299</v>
+        <v>0.2197</v>
       </c>
       <c r="AG9">
-        <v>1.0541</v>
+        <v>0.8136</v>
       </c>
       <c r="AH9">
-        <v>-0.91</v>
+        <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>7.3</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1533,25 +1494,25 @@
         <v>59</v>
       </c>
       <c r="C10">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D10">
-        <v>-104</v>
+        <v>-112</v>
       </c>
       <c r="E10">
-        <v>-122</v>
+        <v>-109</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
       </c>
       <c r="G10">
-        <v>823179</v>
+        <v>823581</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1560,46 +1521,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>0.2265</v>
+        <v>0.3927</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P10">
-        <v>4.26</v>
+        <v>3.79</v>
       </c>
       <c r="Q10">
-        <v>0.1453</v>
+        <v>0.3874</v>
       </c>
       <c r="R10">
-        <v>0.369</v>
+        <v>0.357</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T10">
-        <v>0.1768</v>
+        <v>0.2272</v>
       </c>
       <c r="U10">
-        <v>0.1776</v>
+        <v>0.2221</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>0.1972</v>
+        <v>0.2231</v>
       </c>
       <c r="X10">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y10">
-        <v>0.9127</v>
+        <v>0.9822</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1608,22 +1569,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.43</v>
+        <v>9.56</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="AF10">
-        <v>0.1965</v>
+        <v>0.3908</v>
       </c>
       <c r="AG10">
-        <v>0.8319</v>
+        <v>1.0871</v>
       </c>
       <c r="AH10">
-        <v>0.2</v>
+        <v>-1.07</v>
       </c>
       <c r="AM10">
-        <v>3.63</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1631,28 +1592,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>-113</v>
+        <v>-160</v>
       </c>
       <c r="E11">
-        <v>-113</v>
+        <v>126</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
       </c>
       <c r="G11">
-        <v>823179</v>
+        <v>823581</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1661,46 +1622,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>0.1481</v>
+        <v>0.2312</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="P11">
-        <v>4.58</v>
+        <v>4.32</v>
       </c>
       <c r="Q11">
-        <v>0.1481</v>
+        <v>0.2558</v>
       </c>
       <c r="R11">
-        <v>0.288</v>
+        <v>0.392</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T11">
-        <v>0.169</v>
+        <v>0.1981</v>
       </c>
       <c r="U11">
-        <v>0.1935</v>
+        <v>0.2214</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2048</v>
+        <v>0.2194</v>
       </c>
       <c r="X11">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y11">
-        <v>0.9768</v>
+        <v>0.9836</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1709,22 +1670,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.33</v>
+        <v>5.53</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1481</v>
+        <v>0.2409</v>
       </c>
       <c r="AG11">
-        <v>0.7956</v>
+        <v>0.9475</v>
       </c>
       <c r="AH11">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>2.53</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1734,17 +1695,26 @@
       <c r="B12" t="s">
         <v>63</v>
       </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+      <c r="D12">
+        <v>-162</v>
+      </c>
+      <c r="E12">
+        <v>126</v>
+      </c>
       <c r="F12" t="s">
         <v>64</v>
       </c>
       <c r="G12">
-        <v>822694</v>
+        <v>824879</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1753,46 +1723,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>0.1892</v>
+        <v>0.2487</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="P12">
-        <v>4.34</v>
+        <v>3.84</v>
       </c>
       <c r="Q12">
-        <v>0.1481</v>
+        <v>0.25</v>
       </c>
       <c r="R12">
-        <v>0.351</v>
+        <v>0.39</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T12">
-        <v>0.2362</v>
+        <v>0.2292</v>
       </c>
       <c r="U12">
-        <v>0.2404</v>
+        <v>0.2249</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2065</v>
+        <v>0.2196</v>
       </c>
       <c r="X12">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y12">
-        <v>1.022</v>
+        <v>1.0046</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1801,22 +1771,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.27</v>
+        <v>6.96</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AF12">
-        <v>0.1748</v>
+        <v>0.2492</v>
       </c>
       <c r="AG12">
-        <v>1.1119</v>
+        <v>1.0964</v>
       </c>
       <c r="AH12">
-        <v>0.2</v>
+        <v>-0.57</v>
       </c>
       <c r="AM12">
-        <v>4.47</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1826,17 +1796,26 @@
       <c r="B13" t="s">
         <v>65</v>
       </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+      <c r="D13">
+        <v>130</v>
+      </c>
+      <c r="E13">
+        <v>-151</v>
+      </c>
       <c r="F13" t="s">
         <v>64</v>
       </c>
       <c r="G13">
-        <v>822694</v>
+        <v>824879</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1845,46 +1824,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>0.2242</v>
+        <v>0.3063</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="P13">
-        <v>4.38</v>
+        <v>4.01</v>
       </c>
       <c r="Q13">
-        <v>0.1622</v>
+        <v>0.3707</v>
       </c>
       <c r="R13">
-        <v>0.357</v>
+        <v>0.367</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T13">
-        <v>0.2126</v>
+        <v>0.224</v>
       </c>
       <c r="U13">
-        <v>0.2099</v>
+        <v>0.1967</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>0.2184</v>
+        <v>0.2013</v>
       </c>
       <c r="X13">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y13">
-        <v>1.0209</v>
+        <v>1.0009</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1893,22 +1872,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.37</v>
+        <v>8.34</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="AF13">
-        <v>0.2021</v>
+        <v>0.3299</v>
       </c>
       <c r="AG13">
-        <v>1.0005</v>
+        <v>1.0714</v>
       </c>
       <c r="AH13">
-        <v>0.2</v>
+        <v>-1.07</v>
       </c>
       <c r="AM13">
-        <v>4.57</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1918,17 +1897,26 @@
       <c r="B14" t="s">
         <v>66</v>
       </c>
+      <c r="C14">
+        <v>3.5</v>
+      </c>
+      <c r="D14">
+        <v>-113</v>
+      </c>
+      <c r="E14">
+        <v>-113</v>
+      </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G14">
-        <v>822771</v>
+        <v>823179</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I14">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1937,46 +1925,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>0.2269</v>
+        <v>0.1481</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P14">
-        <v>4.39</v>
+        <v>4.58</v>
       </c>
       <c r="Q14">
-        <v>0.2043</v>
+        <v>0.1481</v>
       </c>
       <c r="R14">
-        <v>0.317</v>
+        <v>0.288</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T14">
-        <v>0.1701</v>
+        <v>0.169</v>
       </c>
       <c r="U14">
-        <v>0.1861</v>
+        <v>0.1935</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>0.2078</v>
+        <v>0.2048</v>
       </c>
       <c r="X14">
-        <v>0.2125</v>
+        <v>0.209</v>
       </c>
       <c r="Y14">
-        <v>0.9625</v>
+        <v>0.9768</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1985,22 +1973,123 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.85</v>
+        <v>2.37</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2197</v>
+        <v>0.1481</v>
       </c>
       <c r="AG14">
-        <v>0.8004</v>
+        <v>0.8087</v>
       </c>
       <c r="AH14">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>4.05</v>
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15">
+        <v>4.5</v>
+      </c>
+      <c r="D15">
+        <v>-104</v>
+      </c>
+      <c r="E15">
+        <v>-122</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15">
+        <v>823179</v>
+      </c>
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15">
+        <v>5.4</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0.2265</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>117</v>
+      </c>
+      <c r="P15">
+        <v>4.26</v>
+      </c>
+      <c r="Q15">
+        <v>0.1453</v>
+      </c>
+      <c r="R15">
+        <v>0.369</v>
+      </c>
+      <c r="S15" t="s">
+        <v>53</v>
+      </c>
+      <c r="T15">
+        <v>0.1768</v>
+      </c>
+      <c r="U15">
+        <v>0.1776</v>
+      </c>
+      <c r="V15">
+        <v>9</v>
+      </c>
+      <c r="W15">
+        <v>0.1972</v>
+      </c>
+      <c r="X15">
+        <v>0.209</v>
+      </c>
+      <c r="Y15">
+        <v>0.9119</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD15">
+        <v>3.48</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF15">
+        <v>0.1965</v>
+      </c>
+      <c r="AG15">
+        <v>0.8456</v>
+      </c>
+      <c r="AH15">
+        <v>0.22</v>
+      </c>
+      <c r="AM15">
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-27.xlsx
+++ b/data/k-props/2026-08-27.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
   <si>
     <t>date</t>
   </si>
@@ -133,46 +133,43 @@
     <t>08/27/2026</t>
   </si>
   <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
     <t>Trevor Rogers</t>
   </si>
   <si>
     <t>Baltimore Orioles @ St. Louis Cardinals</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
     <t>Gordon Graceffo</t>
   </si>
   <si>
-    <t>Role unknown</t>
+    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Hayden Wesneski</t>
   </si>
   <si>
     <t>Houston Astros @ New York Yankees</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>Gerrit Cole</t>
@@ -733,26 +730,17 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>4.5</v>
-      </c>
-      <c r="D2">
-        <v>-118</v>
-      </c>
-      <c r="E2">
-        <v>106</v>
-      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823014</v>
+        <v>822694</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -761,46 +749,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.205</v>
+        <v>0.1801</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="P2">
-        <v>4.19</v>
+        <v>4.43</v>
       </c>
       <c r="Q2">
-        <v>0.2562</v>
+        <v>0.1518</v>
       </c>
       <c r="R2">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1851</v>
+        <v>0.209</v>
       </c>
       <c r="U2">
-        <v>0.1932</v>
+        <v>0.2181</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.1866</v>
+        <v>0.2058</v>
       </c>
       <c r="X2">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y2">
-        <v>0.9253</v>
+        <v>0.9749</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -809,22 +797,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.26</v>
+        <v>3.49</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2243</v>
+        <v>0.1699</v>
       </c>
       <c r="AG2">
-        <v>0.8856</v>
+        <v>0.9584</v>
       </c>
       <c r="AH2">
         <v>0.22</v>
       </c>
       <c r="AM2">
-        <v>4.48</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -835,7 +823,7 @@
         <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>822694</v>
@@ -844,7 +832,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -856,43 +844,43 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0.1832</v>
+        <v>0.2265</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="P3">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="Q3">
-        <v>0.1522</v>
+        <v>0.2018</v>
       </c>
       <c r="R3">
-        <v>0.315</v>
+        <v>0.363</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.209</v>
+        <v>0.228</v>
       </c>
       <c r="U3">
-        <v>0.2181</v>
+        <v>0.2042</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2065</v>
+        <v>0.2184</v>
       </c>
       <c r="X3">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y3">
-        <v>0.9749</v>
+        <v>1.026</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -901,22 +889,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.34</v>
+        <v>4.97</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1735</v>
+        <v>0.2175</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>1.0454</v>
       </c>
       <c r="AH3">
         <v>0.22</v>
       </c>
       <c r="AM3">
-        <v>3.56</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -924,19 +912,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4">
+        <v>-118</v>
+      </c>
+      <c r="E4">
+        <v>106</v>
+      </c>
+      <c r="F4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
       <c r="G4">
-        <v>822694</v>
+        <v>823014</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -945,46 +942,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>0.2232</v>
+        <v>0.209</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="P4">
-        <v>4.4</v>
+        <v>4.21</v>
       </c>
       <c r="Q4">
-        <v>0.1856</v>
+        <v>0.2759</v>
       </c>
       <c r="R4">
-        <v>0.327</v>
+        <v>0.367</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.228</v>
+        <v>0.1851</v>
       </c>
       <c r="U4">
-        <v>0.2042</v>
+        <v>0.1932</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2183</v>
+        <v>0.1883</v>
       </c>
       <c r="X4">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y4">
-        <v>1.026</v>
+        <v>0.9253</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -993,22 +990,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.79</v>
+        <v>4.25</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2109</v>
+        <v>0.2335</v>
       </c>
       <c r="AG4">
-        <v>1.0908</v>
+        <v>0.8487</v>
       </c>
       <c r="AH4">
         <v>0.22</v>
       </c>
       <c r="AM4">
-        <v>5.01</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1019,7 +1016,7 @@
         <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>823014</v>
@@ -1028,7 +1025,7 @@
         <v>50</v>
       </c>
       <c r="I5">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1040,10 +1037,22 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.1502</v>
+        <v>0.1603</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>3.99</v>
+        <v>3.95</v>
+      </c>
+      <c r="Q5">
+        <v>0.4444</v>
+      </c>
+      <c r="R5">
+        <v>0.043</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1058,10 +1067,10 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2361</v>
+        <v>0.2369</v>
       </c>
       <c r="X5">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y5">
         <v>1.0654</v>
@@ -1073,22 +1082,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.61</v>
+        <v>2.62</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1502</v>
+        <v>0.1725</v>
       </c>
       <c r="AG5">
-        <v>1.2541</v>
+        <v>1.202</v>
       </c>
       <c r="AH5">
         <v>0.22</v>
       </c>
       <c r="AM5">
-        <v>3.83</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1147,13 +1156,13 @@
         <v>0.361</v>
       </c>
       <c r="S6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2366</v>
+        <v>0.2455</v>
       </c>
       <c r="U6">
-        <v>0.245</v>
+        <v>0.2547</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1162,10 +1171,10 @@
         <v>0.2467</v>
       </c>
       <c r="X6">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y6">
-        <v>0.9947</v>
+        <v>0.953</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1174,7 +1183,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.95</v>
+        <v>4.72</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1183,13 +1192,13 @@
         <v>0.1947</v>
       </c>
       <c r="AG6">
-        <v>1.1319</v>
+        <v>1.1258</v>
       </c>
       <c r="AH6">
         <v>0.22</v>
       </c>
       <c r="AM6">
-        <v>5.17</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1197,7 +1206,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1248,25 +1257,25 @@
         <v>0.377</v>
       </c>
       <c r="S7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2222</v>
+        <v>0.2174</v>
       </c>
       <c r="U7">
-        <v>0.2138</v>
+        <v>0.2144</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>0.2194</v>
       </c>
       <c r="X7">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y7">
-        <v>0.994</v>
+        <v>0.9915</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1275,22 +1284,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.74</v>
+        <v>6.31</v>
       </c>
       <c r="AE7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AF7">
         <v>0.2716</v>
       </c>
       <c r="AG7">
-        <v>1.0628</v>
+        <v>0.9969</v>
       </c>
       <c r="AH7">
         <v>-0.57</v>
       </c>
       <c r="AM7">
-        <v>6.17</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1298,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1310,7 +1319,7 @@
         <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>822771</v>
@@ -1349,13 +1358,13 @@
         <v>0.388</v>
       </c>
       <c r="S8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1891</v>
+        <v>0.1797</v>
       </c>
       <c r="U8">
-        <v>0.1766</v>
+        <v>0.1616</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1364,10 +1373,10 @@
         <v>0.2092</v>
       </c>
       <c r="X8">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y8">
-        <v>0.981</v>
+        <v>0.9309</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1376,7 +1385,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.56</v>
+        <v>3.94</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1385,13 +1394,13 @@
         <v>0.2161</v>
       </c>
       <c r="AG8">
-        <v>0.9045</v>
+        <v>0.8237</v>
       </c>
       <c r="AH8">
         <v>0.22</v>
       </c>
       <c r="AM8">
-        <v>4.78</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1399,10 +1408,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>822771</v>
@@ -1441,13 +1450,13 @@
         <v>0.317</v>
       </c>
       <c r="S9" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T9">
         <v>0.1701</v>
       </c>
       <c r="U9">
-        <v>0.1861</v>
+        <v>0.1849</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1456,10 +1465,10 @@
         <v>0.2078</v>
       </c>
       <c r="X9">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y9">
-        <v>0.9637</v>
+        <v>0.9477</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1468,7 +1477,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1477,13 +1486,13 @@
         <v>0.2197</v>
       </c>
       <c r="AG9">
-        <v>0.8136</v>
+        <v>0.7799</v>
       </c>
       <c r="AH9">
         <v>0.22</v>
       </c>
       <c r="AM9">
-        <v>4.14</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1491,7 +1500,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>8.5</v>
@@ -1503,7 +1512,7 @@
         <v>-109</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>823581</v>
@@ -1542,25 +1551,25 @@
         <v>0.357</v>
       </c>
       <c r="S10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2272</v>
+        <v>0.2386</v>
       </c>
       <c r="U10">
-        <v>0.2221</v>
+        <v>0.2361</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>0.2231</v>
       </c>
       <c r="X10">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y10">
-        <v>0.9822</v>
+        <v>1.0166</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1569,22 +1578,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>9.56</v>
+        <v>9.96</v>
       </c>
       <c r="AE10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF10">
         <v>0.3908</v>
       </c>
       <c r="AG10">
-        <v>1.0871</v>
+        <v>1.0938</v>
       </c>
       <c r="AH10">
         <v>-1.07</v>
       </c>
       <c r="AM10">
-        <v>8.49</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1592,7 +1601,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1604,7 +1613,7 @@
         <v>126</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>823581</v>
@@ -1643,13 +1652,13 @@
         <v>0.392</v>
       </c>
       <c r="S11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.1981</v>
+        <v>0.1975</v>
       </c>
       <c r="U11">
-        <v>0.2214</v>
+        <v>0.2088</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1658,10 +1667,10 @@
         <v>0.2194</v>
       </c>
       <c r="X11">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y11">
-        <v>0.9836</v>
+        <v>0.88</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1670,7 +1679,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.53</v>
+        <v>4.73</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1679,13 +1688,13 @@
         <v>0.2409</v>
       </c>
       <c r="AG11">
-        <v>0.9475</v>
+        <v>0.9055</v>
       </c>
       <c r="AH11">
         <v>0.22</v>
       </c>
       <c r="AM11">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1693,7 +1702,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>5.5</v>
@@ -1705,7 +1714,7 @@
         <v>126</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>824879</v>
@@ -1744,13 +1753,13 @@
         <v>0.39</v>
       </c>
       <c r="S12" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2292</v>
+        <v>0.2266</v>
       </c>
       <c r="U12">
-        <v>0.2249</v>
+        <v>0.2174</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1759,10 +1768,10 @@
         <v>0.2196</v>
       </c>
       <c r="X12">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y12">
-        <v>1.0046</v>
+        <v>0.9917</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1771,22 +1780,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>6.96</v>
+        <v>6.51</v>
       </c>
       <c r="AE12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AF12">
         <v>0.2492</v>
       </c>
       <c r="AG12">
-        <v>1.0964</v>
+        <v>1.0392</v>
       </c>
       <c r="AH12">
         <v>-0.57</v>
       </c>
       <c r="AM12">
-        <v>6.39</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1794,7 +1803,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>7.5</v>
@@ -1806,7 +1815,7 @@
         <v>-151</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>824879</v>
@@ -1845,25 +1854,25 @@
         <v>0.367</v>
       </c>
       <c r="S13" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.224</v>
+        <v>0.2158</v>
       </c>
       <c r="U13">
-        <v>0.1967</v>
+        <v>0.2026</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>0.2013</v>
       </c>
       <c r="X13">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y13">
-        <v>1.0009</v>
+        <v>0.9741</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1872,22 +1881,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>8.34</v>
+        <v>7.49</v>
       </c>
       <c r="AE13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF13">
         <v>0.3299</v>
       </c>
       <c r="AG13">
-        <v>1.0714</v>
+        <v>0.9893</v>
       </c>
       <c r="AH13">
         <v>-1.07</v>
       </c>
       <c r="AM13">
-        <v>7.27</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1895,7 +1904,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>3.5</v>
@@ -1907,13 +1916,13 @@
         <v>-113</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>823179</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I14">
         <v>4.4</v>
@@ -1946,25 +1955,25 @@
         <v>0.288</v>
       </c>
       <c r="S14" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.169</v>
+        <v>0.2921</v>
       </c>
       <c r="U14">
-        <v>0.1935</v>
+        <v>0.2571</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>0.2048</v>
       </c>
       <c r="X14">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y14">
-        <v>0.9768</v>
+        <v>1.0025</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1973,7 +1982,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>2.37</v>
+        <v>4.03</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -1982,13 +1991,13 @@
         <v>0.1481</v>
       </c>
       <c r="AG14">
-        <v>0.8087</v>
+        <v>1.3394</v>
       </c>
       <c r="AH14">
         <v>0.22</v>
       </c>
       <c r="AM14">
-        <v>2.59</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1996,7 +2005,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2008,7 +2017,7 @@
         <v>-122</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>823179</v>
@@ -2047,13 +2056,13 @@
         <v>0.369</v>
       </c>
       <c r="S15" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.1768</v>
+        <v>0.1858</v>
       </c>
       <c r="U15">
-        <v>0.1776</v>
+        <v>0.1834</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -2062,10 +2071,10 @@
         <v>0.1972</v>
       </c>
       <c r="X15">
-        <v>0.209</v>
+        <v>0.2181</v>
       </c>
       <c r="Y15">
-        <v>0.9119</v>
+        <v>0.88</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2074,7 +2083,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2083,13 +2092,13 @@
         <v>0.1965</v>
       </c>
       <c r="AG15">
-        <v>0.8456</v>
+        <v>0.852</v>
       </c>
       <c r="AH15">
         <v>0.22</v>
       </c>
       <c r="AM15">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-27.xlsx
+++ b/data/k-props/2026-08-27.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="73">
   <si>
     <t>date</t>
   </si>
@@ -160,6 +160,9 @@
     <t>Baltimore Orioles @ St. Louis Cardinals</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>Gordon Graceffo</t>
   </si>
   <si>
@@ -175,6 +178,9 @@
     <t>Gerrit Cole</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
     <t>6-7</t>
   </si>
   <si>
@@ -208,6 +214,9 @@
     <t>Chris Sale</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>Jose Cabrera</t>
   </si>
   <si>
@@ -215,6 +224,9 @@
   </si>
   <si>
     <t>Limited starter</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>Landen Roupp</t>
@@ -983,8 +995,14 @@
       <c r="Y4">
         <v>0.9253</v>
       </c>
+      <c r="Z4">
+        <v>7</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AB4">
+        <v>-0.03</v>
       </c>
       <c r="AC4" t="s">
         <v>44</v>
@@ -1003,6 +1021,18 @@
       </c>
       <c r="AH4">
         <v>0.22</v>
+      </c>
+      <c r="AI4">
+        <v>2.75</v>
+      </c>
+      <c r="AJ4">
+        <v>2.75</v>
+      </c>
+      <c r="AK4">
+        <v>2.53</v>
+      </c>
+      <c r="AL4">
+        <v>2.53</v>
       </c>
       <c r="AM4">
         <v>4.47</v>
@@ -1013,7 +1043,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -1022,7 +1052,7 @@
         <v>823014</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -1105,7 +1135,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1117,7 +1147,7 @@
         <v>-170</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>823503</v>
@@ -1176,8 +1206,14 @@
       <c r="Y6">
         <v>0.953</v>
       </c>
+      <c r="Z6">
+        <v>6</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AB6">
+        <v>0.44</v>
       </c>
       <c r="AC6" t="s">
         <v>44</v>
@@ -1196,6 +1232,18 @@
       </c>
       <c r="AH6">
         <v>0.22</v>
+      </c>
+      <c r="AI6">
+        <v>1.28</v>
+      </c>
+      <c r="AJ6">
+        <v>1.28</v>
+      </c>
+      <c r="AK6">
+        <v>1.06</v>
+      </c>
+      <c r="AL6">
+        <v>1.06</v>
       </c>
       <c r="AM6">
         <v>4.94</v>
@@ -1206,7 +1254,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1218,7 +1266,7 @@
         <v>-113</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>823503</v>
@@ -1277,8 +1325,14 @@
       <c r="Y7">
         <v>0.9915</v>
       </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="AB7">
+        <v>0.24</v>
       </c>
       <c r="AC7" t="s">
         <v>44</v>
@@ -1287,7 +1341,7 @@
         <v>6.31</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AF7">
         <v>0.2716</v>
@@ -1297,6 +1351,18 @@
       </c>
       <c r="AH7">
         <v>-0.57</v>
+      </c>
+      <c r="AI7">
+        <v>-1.31</v>
+      </c>
+      <c r="AJ7">
+        <v>1.31</v>
+      </c>
+      <c r="AK7">
+        <v>-0.74</v>
+      </c>
+      <c r="AL7">
+        <v>0.74</v>
       </c>
       <c r="AM7">
         <v>5.74</v>
@@ -1307,7 +1373,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1319,7 +1385,7 @@
         <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>822771</v>
@@ -1378,8 +1444,14 @@
       <c r="Y8">
         <v>0.9309</v>
       </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="AB8">
+        <v>-0.34</v>
       </c>
       <c r="AC8" t="s">
         <v>44</v>
@@ -1398,6 +1470,18 @@
       </c>
       <c r="AH8">
         <v>0.22</v>
+      </c>
+      <c r="AI8">
+        <v>-0.94</v>
+      </c>
+      <c r="AJ8">
+        <v>0.94</v>
+      </c>
+      <c r="AK8">
+        <v>-1.16</v>
+      </c>
+      <c r="AL8">
+        <v>1.16</v>
       </c>
       <c r="AM8">
         <v>4.16</v>
@@ -1408,10 +1492,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>822771</v>
@@ -1500,7 +1584,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>8.5</v>
@@ -1512,7 +1596,7 @@
         <v>-109</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>823581</v>
@@ -1571,8 +1655,14 @@
       <c r="Y10">
         <v>1.0166</v>
       </c>
+      <c r="Z10">
+        <v>6</v>
+      </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="AB10">
+        <v>0.39</v>
       </c>
       <c r="AC10" t="s">
         <v>44</v>
@@ -1581,7 +1671,7 @@
         <v>9.96</v>
       </c>
       <c r="AE10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AF10">
         <v>0.3908</v>
@@ -1591,6 +1681,18 @@
       </c>
       <c r="AH10">
         <v>-1.07</v>
+      </c>
+      <c r="AI10">
+        <v>-3.96</v>
+      </c>
+      <c r="AJ10">
+        <v>3.96</v>
+      </c>
+      <c r="AK10">
+        <v>-2.89</v>
+      </c>
+      <c r="AL10">
+        <v>2.89</v>
       </c>
       <c r="AM10">
         <v>8.89</v>
@@ -1601,7 +1703,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1613,7 +1715,7 @@
         <v>126</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>823581</v>
@@ -1672,8 +1774,14 @@
       <c r="Y11">
         <v>0.88</v>
       </c>
+      <c r="Z11">
+        <v>3</v>
+      </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="AB11">
+        <v>0.45</v>
       </c>
       <c r="AC11" t="s">
         <v>44</v>
@@ -1692,6 +1800,18 @@
       </c>
       <c r="AH11">
         <v>0.22</v>
+      </c>
+      <c r="AI11">
+        <v>-1.73</v>
+      </c>
+      <c r="AJ11">
+        <v>1.73</v>
+      </c>
+      <c r="AK11">
+        <v>-1.95</v>
+      </c>
+      <c r="AL11">
+        <v>1.95</v>
       </c>
       <c r="AM11">
         <v>4.95</v>
@@ -1702,7 +1822,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>5.5</v>
@@ -1714,7 +1834,7 @@
         <v>126</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>824879</v>
@@ -1773,8 +1893,14 @@
       <c r="Y12">
         <v>0.9917</v>
       </c>
+      <c r="Z12">
+        <v>8</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AB12">
+        <v>0.44</v>
       </c>
       <c r="AC12" t="s">
         <v>44</v>
@@ -1783,7 +1909,7 @@
         <v>6.51</v>
       </c>
       <c r="AE12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AF12">
         <v>0.2492</v>
@@ -1793,6 +1919,18 @@
       </c>
       <c r="AH12">
         <v>-0.57</v>
+      </c>
+      <c r="AI12">
+        <v>1.49</v>
+      </c>
+      <c r="AJ12">
+        <v>1.49</v>
+      </c>
+      <c r="AK12">
+        <v>2.06</v>
+      </c>
+      <c r="AL12">
+        <v>2.06</v>
       </c>
       <c r="AM12">
         <v>5.94</v>
@@ -1803,7 +1941,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>7.5</v>
@@ -1815,7 +1953,7 @@
         <v>-151</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>824879</v>
@@ -1874,17 +2012,23 @@
       <c r="Y13">
         <v>0.9741</v>
       </c>
+      <c r="Z13">
+        <v>11</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AB13">
+        <v>-1.08</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AD13">
         <v>7.49</v>
       </c>
       <c r="AE13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AF13">
         <v>0.3299</v>
@@ -1894,6 +2038,18 @@
       </c>
       <c r="AH13">
         <v>-1.07</v>
+      </c>
+      <c r="AI13">
+        <v>3.51</v>
+      </c>
+      <c r="AJ13">
+        <v>3.51</v>
+      </c>
+      <c r="AK13">
+        <v>4.58</v>
+      </c>
+      <c r="AL13">
+        <v>4.58</v>
       </c>
       <c r="AM13">
         <v>6.42</v>
@@ -1904,7 +2060,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C14">
         <v>3.5</v>
@@ -1916,13 +2072,13 @@
         <v>-113</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>823179</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>4.4</v>
@@ -1975,11 +2131,17 @@
       <c r="Y14">
         <v>1.0025</v>
       </c>
+      <c r="Z14">
+        <v>4</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AB14">
+        <v>0.75</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="AD14">
         <v>4.03</v>
@@ -1995,6 +2157,18 @@
       </c>
       <c r="AH14">
         <v>0.22</v>
+      </c>
+      <c r="AI14">
+        <v>-0.03</v>
+      </c>
+      <c r="AJ14">
+        <v>0.03</v>
+      </c>
+      <c r="AK14">
+        <v>-0.25</v>
+      </c>
+      <c r="AL14">
+        <v>0.25</v>
       </c>
       <c r="AM14">
         <v>4.25</v>
@@ -2005,7 +2179,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2017,7 +2191,7 @@
         <v>-122</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>823179</v>
@@ -2076,11 +2250,17 @@
       <c r="Y15">
         <v>0.88</v>
       </c>
+      <c r="Z15">
+        <v>3</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="AB15">
+        <v>-0.9</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="AD15">
         <v>3.38</v>
@@ -2096,6 +2276,18 @@
       </c>
       <c r="AH15">
         <v>0.22</v>
+      </c>
+      <c r="AI15">
+        <v>-0.38</v>
+      </c>
+      <c r="AJ15">
+        <v>0.38</v>
+      </c>
+      <c r="AK15">
+        <v>-0.6</v>
+      </c>
+      <c r="AL15">
+        <v>0.6</v>
       </c>
       <c r="AM15">
         <v>3.6</v>
